--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,345 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130017995</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långängen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>653526</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683094</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130017982</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storsvedden, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>653484</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683047</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130017996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92028</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storsvedden, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>653457</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6682980</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130017995</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130017996</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130017995</v>
+        <v>130017982</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,37 +1058,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långängen, Upl</t>
+          <t>Storsvedden, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653526</v>
+        <v>653484</v>
       </c>
       <c r="R5" t="n">
-        <v>6683094</v>
+        <v>6683047</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1120,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130017982</v>
+        <v>130017995</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>91606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,46 +1177,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storsvedden, Upl</t>
+          <t>Långängen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653484</v>
+        <v>653526</v>
       </c>
       <c r="R6" t="n">
-        <v>6683047</v>
+        <v>6683094</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>130017995</v>
       </c>
       <c r="B6" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130017996</v>
       </c>
       <c r="B7" t="n">
-        <v>92029</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>130017995</v>
       </c>
       <c r="B6" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130017996</v>
       </c>
       <c r="B7" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130017982</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>130017995</v>
       </c>
       <c r="B6" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>130017996</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130017982</v>
+        <v>130017995</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,46 +1058,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storsvedden, Upl</t>
+          <t>Långängen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653484</v>
+        <v>653526</v>
       </c>
       <c r="R5" t="n">
-        <v>6683047</v>
+        <v>6683094</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1129,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130017995</v>
+        <v>130017982</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,37 +1168,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långängen, Upl</t>
+          <t>Storsvedden, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653526</v>
+        <v>653484</v>
       </c>
       <c r="R6" t="n">
-        <v>6683094</v>
+        <v>6683047</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115385504</v>
+        <v>130017995</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653463</v>
+        <v>653526</v>
       </c>
       <c r="R2" t="n">
-        <v>6683100</v>
+        <v>6683094</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115385505</v>
+        <v>130017996</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,35 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653441</v>
+        <v>653457</v>
       </c>
       <c r="R3" t="n">
-        <v>6683088</v>
+        <v>6682980</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -881,22 +853,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116072893</v>
+        <v>130017982</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,23 +932,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långängen, Upl</t>
+          <t>Storsvedden, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653582</v>
+        <v>653484</v>
       </c>
       <c r="R4" t="n">
-        <v>6683182</v>
+        <v>6683047</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,37 +1014,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130017995</v>
+        <v>115385504</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653526</v>
+        <v>653463</v>
       </c>
       <c r="R5" t="n">
-        <v>6683094</v>
+        <v>6683100</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1115,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130017982</v>
+        <v>115385505</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1194,7 +1170,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1204,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653484</v>
+        <v>653441</v>
       </c>
       <c r="R6" t="n">
-        <v>6683047</v>
+        <v>6683088</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1234,22 +1210,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130017996</v>
+        <v>116072893</v>
       </c>
       <c r="B7" t="n">
-        <v>92151</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,40 +1263,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storsvedden, Upl</t>
+          <t>Långängen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>653457</v>
+        <v>653582</v>
       </c>
       <c r="R7" t="n">
-        <v>6682980</v>
+        <v>6683182</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,22 +1329,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54831-2025 artfynd.xlsx
+++ b/artfynd/A 54831-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130017995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115385504</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115385505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,8 +1398,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116072893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>